--- a/src/Tests/Samples.VerifyWorkbook.verified.xlsx
+++ b/src/Tests/Samples.VerifyWorkbook.verified.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="New Sheet" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
+    <sheet name="New Sheet" sheetId="2" r:id="DeterministicId5"/>
   </sheets>
   <definedNames/>
   <calcPr fullCalcOnLoad="1"/>
